--- a/04_DESIGN_TABLES/DesignTable_2603.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2603.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
@@ -1356,7 +1356,11 @@
           <t>MS51510E corroborates matched sizes (13-row, all legs equal +/-.030); JIC ends VERIFIED (MS33656J)</t>
         </is>
       </c>
-      <c r="P14" s="3" t="inlineStr"/>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on Y@REF=0.75~0.750; D1@BORE=0.39~0.391; D2@BORE=0.39~0.391; D3@BORE=0.3~0.297</t>
+        </is>
+      </c>
       <c r="Q14" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -2625,7 +2629,7 @@
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
@@ -2633,7 +2637,11 @@
           <t>MS51510E corroborates matched sizes (13-row, all legs equal +/-.030); JIC ends VERIFIED (MS33656J)</t>
         </is>
       </c>
-      <c r="P33" s="3" t="inlineStr"/>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on Y@REF=1.31~1.312; D1@BORE=0.84~0.844; D2@BORE=0.84~0.844; D3@BORE=0.61~0.609</t>
+        </is>
+      </c>
       <c r="Q33" t="inlineStr">
         <is>
           <t>BUILD</t>

--- a/04_DESIGN_TABLES/DesignTable_2603.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2603.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R44"/>
+  <dimension ref="A1:S44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -559,6 +559,11 @@
           <t>$PRP@OMiSKU</t>
         </is>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>$PRP@DimSource</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -3332,24 +3337,59 @@
           <t>2603-02-02-02-FG</t>
         </is>
       </c>
+      <c r="B44" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0.062</v>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>2603-02-02-02-FG</t>
         </is>
       </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>5/16-24 x 5/16-24 x 5/16-24</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>OMi catalog SKU; legs / flats / bores: OMi WebsitePartsInfo2026 Items row 821 (= Brennan TFA p.49 TFA-p049-t03, one source); NO Air-Way row for this size; JIC ends MS33656J (end library)</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source</t>
+          <t>2026-10-20 (batch 19 E_gen, A7): sizes from OMi Items (= Brennan TFA p.49), end details from the end library</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
@@ -3360,6 +3400,11 @@
       <c r="R44" t="inlineStr">
         <is>
           <t>2603-02-02-02-FG</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>OMI</t>
         </is>
       </c>
     </row>
